--- a/Trading Analysis/RFQ_1130350_Sourcing_Summary.xlsx
+++ b/Trading Analysis/RFQ_1130350_Sourcing_Summary.xlsx
@@ -3,8 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="No Broker Inventory" sheetId="2" r:id="rId2"/>
+    <sheet name="RFQs Sent" sheetId="1" r:id="rId1"/>
+    <sheet name="By Supplier" sheetId="2" r:id="rId2"/>
+    <sheet name="By MPN" sheetId="3" r:id="rId3"/>
+    <sheet name="Stats" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -398,449 +400,4067 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E144"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>RFQ 1130350 Broker Sourcing Summary</v>
+        <v>MPN</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Region</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Qty Requested</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Date: 2026-03-10</v>
+        <v>TPS63060DSCT</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ECR Electronics Ltd.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D2">
+        <v>1950</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Purpose: Excess inventory valuation</v>
+        <v>TPS63060DSCT</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Goldney Electronics S.L.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D3">
+        <v>1950</v>
+      </c>
+      <c r="E3" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TPS63060DSCT</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Avant Electronics Limited</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D4">
+        <v>1950</v>
+      </c>
+      <c r="E4" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Batch</v>
+        <v>ADG734BRUZ</v>
       </c>
       <c r="B5" t="str">
-        <v>Parts</v>
+        <v>Sogenti GmbH</v>
       </c>
       <c r="C5" t="str">
-        <v>RFQs Sent</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Notes</v>
+        <v>Europe</v>
+      </c>
+      <c r="D5">
+        <v>1450</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1</v>
+        <v>ADG734BRUZ</v>
       </c>
       <c r="B6" t="str">
-        <v>#1-15</v>
+        <v>Tectiva</v>
       </c>
       <c r="C6" t="str">
-        <v>~10</v>
-      </c>
-      <c r="D6" t="str">
-        <v>CN6880LP held (price error)</v>
+        <v>Europe</v>
+      </c>
+      <c r="D6">
+        <v>1450</v>
+      </c>
+      <c r="E6" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2</v>
+        <v>LT1618EDD</v>
       </c>
       <c r="B7" t="str">
-        <v>#16-30</v>
+        <v>Component Electronics Inc.</v>
       </c>
       <c r="C7" t="str">
-        <v>~15</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Completed</v>
+        <v>Americas</v>
+      </c>
+      <c r="D7">
+        <v>1250</v>
+      </c>
+      <c r="E7" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3</v>
+        <v>LT1618EDD</v>
       </c>
       <c r="B8" t="str">
-        <v>#31-45</v>
+        <v>CCI Europe GmbH</v>
       </c>
       <c r="C8" t="str">
-        <v>19</v>
-      </c>
-      <c r="D8" t="str">
-        <v>8 variants skipped</v>
+        <v>Europe</v>
+      </c>
+      <c r="D8">
+        <v>600</v>
+      </c>
+      <c r="E8" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4</v>
+        <v>LT3070EUFD</v>
       </c>
       <c r="B9" t="str">
-        <v>#46-60</v>
+        <v>Inventory Management Partners</v>
       </c>
       <c r="C9" t="str">
-        <v>30</v>
-      </c>
-      <c r="D9" t="str">
-        <v>4 no inventory, 4 variants</v>
+        <v>Americas</v>
+      </c>
+      <c r="D9">
+        <v>148</v>
+      </c>
+      <c r="E9" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5</v>
+        <v>LT3070EUFD</v>
       </c>
       <c r="B10" t="str">
-        <v>#61-75</v>
+        <v>Select Technology Inc.</v>
       </c>
       <c r="C10" t="str">
-        <v>34</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2 no inventory, 5 variants</v>
+        <v>Americas</v>
+      </c>
+      <c r="D10">
+        <v>275</v>
+      </c>
+      <c r="E10" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6</v>
+        <v>LT3070EUFD</v>
       </c>
       <c r="B11" t="str">
-        <v>#76-90</v>
+        <v>Semitech Inc.</v>
       </c>
       <c r="C11" t="str">
-        <v>37</v>
-      </c>
-      <c r="D11" t="str">
-        <v>3 no inventory, 4 variants</v>
+        <v>Americas</v>
+      </c>
+      <c r="D11">
+        <v>146</v>
+      </c>
+      <c r="E11" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>7</v>
+        <v>LT3080EDD-1</v>
       </c>
       <c r="B12" t="str">
-        <v>#91-101</v>
+        <v>Atlantic Semiconductor Corp.</v>
       </c>
       <c r="C12" t="str">
-        <v>23</v>
-      </c>
-      <c r="D12" t="str">
-        <v>3 no inventory, 3 variants</v>
+        <v>Americas</v>
+      </c>
+      <c r="D12">
+        <v>1250</v>
+      </c>
+      <c r="E12" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TOTAL</v>
+        <v>LT3080EDD-1</v>
       </c>
       <c r="B13" t="str">
-        <v>101 line items</v>
+        <v>Prism Electronics</v>
       </c>
       <c r="C13" t="str">
-        <v>~168</v>
-      </c>
-      <c r="D13" t="str">
-        <v>59 base MPNs sourced</v>
+        <v>Americas</v>
+      </c>
+      <c r="D13">
+        <v>525</v>
+      </c>
+      <c r="E13" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LT3080EDD-1</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Inventory Management Partners</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D14">
+        <v>775</v>
+      </c>
+      <c r="E14" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Key Stats</v>
+        <v>LT3080EDD-1</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Tomark Electronics Ltd</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D15">
+        <v>150</v>
+      </c>
+      <c r="E15" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unique suppliers contacted</v>
+        <v>LT3080EDD-1</v>
       </c>
       <c r="B16" t="str">
-        <v>80+</v>
+        <v>Ganir Tech Ltd.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D16">
+        <v>1250</v>
+      </c>
+      <c r="E16" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Max RFQs per supplier</v>
+        <v>LT3973IMSE</v>
       </c>
       <c r="B17" t="str">
-        <v>2 (fatigue limit)</v>
+        <v>Abstract Electronics</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D17">
+        <v>200</v>
+      </c>
+      <c r="E17" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Packaging variants skipped</v>
+        <v>LT3973IMSE</v>
       </c>
       <c r="B18" t="str">
-        <v>42</v>
+        <v>ComSIT Distribution GmbH</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Parts with no broker inventory</v>
+        <v>LTC4263IDE</v>
       </c>
       <c r="B19" t="str">
-        <v>12</v>
+        <v>GC Components Ltd</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D19">
+        <v>171</v>
+      </c>
+      <c r="E19" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LTC4263IDE</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ComSIT Distribution GmbH</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D20">
+        <v>100</v>
+      </c>
+      <c r="E20" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Workflow Fixes Applied</v>
+        <v>LTC4357IMS8</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Husky Intl. Electronics, Inc.</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D21">
+        <v>300</v>
+      </c>
+      <c r="E21" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1. Strict MPN matching in franchise screening</v>
+        <v>LTC4357IMS8</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Voyager Components</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D22">
+        <v>90</v>
+      </c>
+      <c r="E22" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2. Min order value filtering (abundant=0.2x, scarce=0.7x)</v>
+        <v>LTC4357IMS8</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Microfarads</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D23">
+        <v>575</v>
+      </c>
+      <c r="E23" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>3. Supplier fatigue tracking (max 2/supplier)</v>
+        <v>LTM8026IV</v>
+      </c>
+      <c r="B24" t="str">
+        <v>LIBRA Elektronik GmbH</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="E24" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>4. Packaging variant deduplication</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B25" t="str">
+        <v>IC-Tronix Inc.</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D25">
+        <v>580</v>
+      </c>
+      <c r="E25" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>5. Chip 1 Exchange exclusion</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B26" t="str">
+        <v>YBS Enterprises dbElectro-Comm</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D26">
+        <v>580</v>
+      </c>
+      <c r="E26" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SVT</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D27">
+        <v>580</v>
+      </c>
+      <c r="E27" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Next Steps</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Abstract Electronics</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D28">
+        <v>525</v>
+      </c>
+      <c r="E28" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1. Monitor VQ inbox for responses (3-5 days)</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Inelco Components S.L.</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D29">
+        <v>580</v>
+      </c>
+      <c r="E29" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2. Load VQs via VQ Parser workflow</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B30" t="str">
+        <v>EXC GmbH</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D30">
+        <v>580</v>
+      </c>
+      <c r="E30" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>3. Generate valuation report</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Eurodis Components</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D31">
+        <v>580</v>
+      </c>
+      <c r="E31" t="str">
+        <v>SENT</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>4. CN6880LP needs manual sourcing</v>
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B32" t="str">
+        <v>CHANETECH</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D32">
+        <v>580</v>
+      </c>
+      <c r="E32" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>MAX3318EIPW</v>
+      </c>
+      <c r="B33" t="str">
+        <v>A&amp;K Electronics</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D33">
+        <v>1100</v>
+      </c>
+      <c r="E33" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>MAX3318EIPW</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Eptix Inc.</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D34">
+        <v>140</v>
+      </c>
+      <c r="E34" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>MAX3318EIPW</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TCX Micro S.L.</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D35">
+        <v>775</v>
+      </c>
+      <c r="E35" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>12106D476KAT2A</v>
+      </c>
+      <c r="B36" t="str">
+        <v>PC Components (PCC)</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D36">
+        <v>3300</v>
+      </c>
+      <c r="E36" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>12106D476KAT2A</v>
+      </c>
+      <c r="B37" t="str">
+        <v>D.F. Sales Company</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D37">
+        <v>2500</v>
+      </c>
+      <c r="E37" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>12106D476KAT2A</v>
+      </c>
+      <c r="B38" t="str">
+        <v>North Shore Components Inc.</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D38">
+        <v>14000</v>
+      </c>
+      <c r="E38" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>12106D476KAT2A</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Semi Source Inc.</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D39">
+        <v>5100</v>
+      </c>
+      <c r="E39" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B40" t="str">
+        <v>New Advantage Corp</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D40">
+        <v>2000</v>
+      </c>
+      <c r="E40" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Converge LLC</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D41">
+        <v>2000</v>
+      </c>
+      <c r="E41" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Commodity Components</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D42">
+        <v>2000</v>
+      </c>
+      <c r="E42" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Nexus Electronics LLC</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D43">
+        <v>375</v>
+      </c>
+      <c r="E43" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Ganir Tech Ltd.</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D44">
+        <v>2000</v>
+      </c>
+      <c r="E44" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B45" t="str">
+        <v>BESA Technologies GmbH</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D45">
+        <v>725</v>
+      </c>
+      <c r="E45" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B46" t="str">
+        <v>iget Electronics GmbH</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D46">
+        <v>375</v>
+      </c>
+      <c r="E46" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>C1005X5R1C104K</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Elcom Components, Inc.</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D47">
+        <v>18600</v>
+      </c>
+      <c r="E47" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>C1005X5R1C104K</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Atlantic Semiconductor Corp.</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D48">
+        <v>13800</v>
+      </c>
+      <c r="E48" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CY29946AXC</v>
+      </c>
+      <c r="B49" t="str">
+        <v>SVT</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D49">
+        <v>146</v>
+      </c>
+      <c r="E49" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CY29946AXC</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Semi Source Inc.</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D50">
+        <v>675</v>
+      </c>
+      <c r="E50" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>CY29946AXC</v>
+      </c>
+      <c r="B51" t="str">
+        <v>SPM Sales and Solution</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D51">
+        <v>113</v>
+      </c>
+      <c r="E51" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>CY8C3866AXI-040</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Hybrid Electronics</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D52">
+        <v>40</v>
+      </c>
+      <c r="E52" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Converge LLC</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D53">
+        <v>1000</v>
+      </c>
+      <c r="E53" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Touchstone Systems, LLC</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D54">
+        <v>925</v>
+      </c>
+      <c r="E54" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Quest Components</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D55">
+        <v>675</v>
+      </c>
+      <c r="E55" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B56" t="str">
+        <v>ECR Electronics Ltd.</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D56">
+        <v>2300</v>
+      </c>
+      <c r="E56" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Electronic Stock Ltd.</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D57">
+        <v>2300</v>
+      </c>
+      <c r="E57" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Prestocom, Ltd.</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D58">
+        <v>1100</v>
+      </c>
+      <c r="E58" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B59" t="str">
+        <v>J2 Sourcing AB</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D59">
+        <v>850</v>
+      </c>
+      <c r="E59" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>EPM2210F324I5N</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Touchstone Systems, LLC</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D60">
+        <v>50</v>
+      </c>
+      <c r="E60" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>EPM2210F324I5N</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Hybrid Electronics</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D61">
+        <v>20</v>
+      </c>
+      <c r="E61" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>EPM2210F324I5N</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Integrated Electronics Company</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D62">
+        <v>50</v>
+      </c>
+      <c r="E62" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>EPM2210F324I5N</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Classic Components</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D63">
+        <v>45</v>
+      </c>
+      <c r="E63" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>EPM2210F324I5N</v>
+      </c>
+      <c r="B64" t="str">
+        <v>TerraBlock (fka Vecsys)</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D64">
+        <v>50</v>
+      </c>
+      <c r="E64" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>146839-3</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Component Electronics Inc.</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D65">
+        <v>141</v>
+      </c>
+      <c r="E65" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>146839-3</v>
+      </c>
+      <c r="B66" t="str">
+        <v>IBH Elektrotechnik GmbH</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D66">
+        <v>375</v>
+      </c>
+      <c r="E66" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>146839-3</v>
+      </c>
+      <c r="B67" t="str">
+        <v>AG Electronics Limited</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D67">
+        <v>125</v>
+      </c>
+      <c r="E67" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>146839-3</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Ashlea Components Ltd.</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D68">
+        <v>70</v>
+      </c>
+      <c r="E68" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Prism Electronics</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D69">
+        <v>9400</v>
+      </c>
+      <c r="E69" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B70" t="str">
+        <v>FCC (First Choice Components)</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D70">
+        <v>9400</v>
+      </c>
+      <c r="E70" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Quantum Digital Technology</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D71">
+        <v>9400</v>
+      </c>
+      <c r="E71" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B72" t="str">
+        <v>PC Components (PCC)</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D72">
+        <v>1400</v>
+      </c>
+      <c r="E72" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Fly Chips</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D73">
+        <v>7700</v>
+      </c>
+      <c r="E73" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Electronic Stock Ltd.</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D74">
+        <v>7100</v>
+      </c>
+      <c r="E74" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B75" t="str">
+        <v>SM Elektronik</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D75">
+        <v>3000</v>
+      </c>
+      <c r="E75" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Schukat Electronic GmbH</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D76">
+        <v>1800</v>
+      </c>
+      <c r="E76" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>AFBR-709DMZ</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Smith &amp; Associates</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D77">
+        <v>300</v>
+      </c>
+      <c r="E77" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>AFBR-709DMZ</v>
+      </c>
+      <c r="B78" t="str">
+        <v>AER Worldwide</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D78">
+        <v>50</v>
+      </c>
+      <c r="E78" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B79" t="str">
+        <v>FreedomUSA</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D79">
+        <v>3000</v>
+      </c>
+      <c r="E79" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B80" t="str">
+        <v>P&amp;A Components Inc.</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D80">
+        <v>1000</v>
+      </c>
+      <c r="E80" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Maritex Leszek Losin Sp. j.</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D81">
+        <v>9500</v>
+      </c>
+      <c r="E81" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Schukat Electronic GmbH</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D82">
+        <v>4400</v>
+      </c>
+      <c r="E82" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B83" t="str">
+        <v>J.M.P. Electronics, Ltd.</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D83">
+        <v>2000</v>
+      </c>
+      <c r="E83" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B84" t="str">
+        <v>HZD GmbH</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D84">
+        <v>1100</v>
+      </c>
+      <c r="E84" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>FTLX8571D3BCV</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Lemkor Electronics, Inc</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D85">
+        <v>225</v>
+      </c>
+      <c r="E85" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>FTLX8571D3BCV</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Carlin Systems Inc.</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D86">
+        <v>50</v>
+      </c>
+      <c r="E86" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>FTLX8571D3BCV</v>
+      </c>
+      <c r="B87" t="str">
+        <v>I.C. Plus, Inc.</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D87">
+        <v>300</v>
+      </c>
+      <c r="E87" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>FTSH-108-01-L-DV</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Demand Components</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D88">
+        <v>2500</v>
+      </c>
+      <c r="E88" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>FTSH-108-01-L-DV</v>
+      </c>
+      <c r="B89" t="str">
+        <v>NetSource Technology Inc.</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D89">
+        <v>5400</v>
+      </c>
+      <c r="E89" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>FTSH-108-01-L-DV</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Partservice</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D90">
+        <v>1100</v>
+      </c>
+      <c r="E90" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>FTSH-108-01-L-DV</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Fly Chips</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D91">
+        <v>600</v>
+      </c>
+      <c r="E91" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>FTSH-108-01-L-DV</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Component Sense</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D92">
+        <v>5000</v>
+      </c>
+      <c r="E92" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>HX1188FNL</v>
+      </c>
+      <c r="B93" t="str">
+        <v>NexGen Digital, Inc.</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D93">
+        <v>4316</v>
+      </c>
+      <c r="E93" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>HX1188FNL</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Megastar Electronics, Inc.</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D94">
+        <v>775</v>
+      </c>
+      <c r="E94" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>HX1188FNL</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Chip Stock, LLC</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D95">
+        <v>600</v>
+      </c>
+      <c r="E95" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>HX1188FNL</v>
+      </c>
+      <c r="B96" t="str">
+        <v>SM Elektronik</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D96">
+        <v>1200</v>
+      </c>
+      <c r="E96" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>HX1188FNL</v>
+      </c>
+      <c r="B97" t="str">
+        <v>SIE Connect-GreenChips</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D97">
+        <v>550</v>
+      </c>
+      <c r="E97" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>J1011F21PNL</v>
+      </c>
+      <c r="B98" t="str">
+        <v>X-Press Micro, Inc.</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D98">
+        <v>1640</v>
+      </c>
+      <c r="E98" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>J1011F21PNL</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Eurodis Components</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D99">
+        <v>1640</v>
+      </c>
+      <c r="E99" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>J1011F21PNL</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Solsta Limited</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D100">
+        <v>550</v>
+      </c>
+      <c r="E100" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>J1011F21PNL</v>
+      </c>
+      <c r="B101" t="str">
+        <v>J2 Sourcing AB</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D101">
+        <v>1640</v>
+      </c>
+      <c r="E101" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B102" t="str">
+        <v>RLX Solutions Inc.</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D102">
+        <v>775</v>
+      </c>
+      <c r="E102" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Impact Components</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D103">
+        <v>675</v>
+      </c>
+      <c r="E103" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Sonicare Solutions</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D104">
+        <v>175</v>
+      </c>
+      <c r="E104" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B105" t="str">
+        <v>TME</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D105">
+        <v>1800</v>
+      </c>
+      <c r="E105" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B106" t="str">
+        <v>4Source Electronics AG</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D106">
+        <v>300</v>
+      </c>
+      <c r="E106" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Weisbauer Elektronik GmbH</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D107">
+        <v>1200</v>
+      </c>
+      <c r="E107" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Rapid Electronics Ltd.</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D108">
+        <v>425</v>
+      </c>
+      <c r="E108" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>MIC49500WR</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Quest Components</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D109">
+        <v>300</v>
+      </c>
+      <c r="E109" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>MIC49500WR</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Right Parts</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D110">
+        <v>170</v>
+      </c>
+      <c r="E110" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>MIC49500WR</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Maritex Leszek Losin Sp. j.</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D111">
+        <v>1250</v>
+      </c>
+      <c r="E111" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Zilex Electronics Inc.</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D112">
+        <v>900</v>
+      </c>
+      <c r="E112" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Silicon Solutions Inc.</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D113">
+        <v>900</v>
+      </c>
+      <c r="E113" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Diverse Electronics</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D114">
+        <v>900</v>
+      </c>
+      <c r="E114" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B115" t="str">
+        <v>AES - Atlas Electronic Systems</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D115">
+        <v>900</v>
+      </c>
+      <c r="E115" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B116" t="str">
+        <v>LIBRA Elektronik GmbH</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D116">
+        <v>900</v>
+      </c>
+      <c r="E116" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Silicon Solutions LP Europe</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D117">
+        <v>900</v>
+      </c>
+      <c r="E117" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Merefields Electronics</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D118">
+        <v>900</v>
+      </c>
+      <c r="E118" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B119" t="str">
+        <v>A-Source Electronics BV</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D119">
+        <v>225</v>
+      </c>
+      <c r="E119" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>MT28FW02GBBA1HPC-0AAT</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Chip Stock, LLC</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D120">
+        <v>150</v>
+      </c>
+      <c r="E120" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>MT28FW02GBBA1HPC-0AAT</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Aitech Systems Ltd.</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D121">
+        <v>50</v>
+      </c>
+      <c r="E121" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>NFM18PC105R0J3D</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Voyager Components</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D122">
+        <v>12700</v>
+      </c>
+      <c r="E122" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>NFM18PC105R0J3D</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Flex-Com International Ltd.</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D123">
+        <v>78460</v>
+      </c>
+      <c r="E123" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>NFM18PC105R0J3D</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Seba Components</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D124">
+        <v>78460</v>
+      </c>
+      <c r="E124" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>NFM18PC105R0J3D</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Grossenbacher Systeme AG</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D125">
+        <v>10800</v>
+      </c>
+      <c r="E125" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>NFM18PC105R0J3D</v>
+      </c>
+      <c r="B126" t="str">
+        <v>GC Components Ltd</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D126">
+        <v>8300</v>
+      </c>
+      <c r="E126" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B127" t="str">
+        <v>AGS Devices Ltd</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D127">
+        <v>4900</v>
+      </c>
+      <c r="E127" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Right Parts</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D128">
+        <v>4700</v>
+      </c>
+      <c r="E128" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Computer Components Ltd</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D129">
+        <v>2500</v>
+      </c>
+      <c r="E129" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B130" t="str">
+        <v>CVC Components Ltd.</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D130">
+        <v>10000</v>
+      </c>
+      <c r="E130" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B131" t="str">
+        <v>SIE Connect-GreenChips</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D131">
+        <v>3500</v>
+      </c>
+      <c r="E131" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Grossenbacher Systeme AG</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D132">
+        <v>2600</v>
+      </c>
+      <c r="E132" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Omega GTI</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D133">
+        <v>12465</v>
+      </c>
+      <c r="E133" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B134" t="str">
+        <v>NexGen Digital, Inc.</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D134">
+        <v>5000</v>
+      </c>
+      <c r="E134" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B135" t="str">
+        <v>AED Inc.</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D135">
+        <v>2900</v>
+      </c>
+      <c r="E135" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B136" t="str">
+        <v>IC-Tronix Inc.</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D136">
+        <v>2500</v>
+      </c>
+      <c r="E136" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B137" t="str">
+        <v>SECO spa</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D137">
+        <v>12465</v>
+      </c>
+      <c r="E137" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B138" t="str">
+        <v>ICL Electronic-Bauteil-Service</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D138">
+        <v>12465</v>
+      </c>
+      <c r="E138" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Avant Electronics Limited</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D139">
+        <v>1800</v>
+      </c>
+      <c r="E139" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>S102M59Z5UU83L0R</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Dot Comps Electronics Inc.</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D140">
+        <v>5</v>
+      </c>
+      <c r="E140" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>S102M59Z5UU83L0R</v>
+      </c>
+      <c r="B141" t="str">
+        <v>TME</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D141">
+        <v>50</v>
+      </c>
+      <c r="E141" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>TPS63060DSC</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Dark Horse Electronics</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="D142">
+        <v>4175</v>
+      </c>
+      <c r="E142" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>TPS63060DSC</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Tencell</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D143">
+        <v>3000</v>
+      </c>
+      <c r="E143" t="str">
+        <v>SENT</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>TPS63060DSC</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Sternenhof Electronics</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="D144">
+        <v>1000</v>
+      </c>
+      <c r="E144" t="str">
+        <v>SENT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E144"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C111"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>#</v>
+        <v>Supplier</v>
       </c>
       <c r="B1" t="str">
-        <v>MPN</v>
+        <v>Region</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Franchise Status</v>
+        <v>RFQ Count</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>56</v>
+      <c r="A2" t="str">
+        <v>ECR Electronics Ltd.</v>
       </c>
       <c r="B2" t="str">
-        <v>C1812C335K1RACAUTO</v>
-      </c>
-      <c r="C2" t="str">
-        <v>KEMET Auto Cap</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Franchise available</v>
+        <v>Europe</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>57</v>
+      <c r="A3" t="str">
+        <v>Avant Electronics Limited</v>
       </c>
       <c r="B3" t="str">
-        <v>CB2V53I100M0000</v>
-      </c>
-      <c r="C3" t="str">
-        <v>CTS Crystal</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Franchise available</v>
+        <v>Europe</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>58</v>
+      <c r="A4" t="str">
+        <v>Component Electronics Inc.</v>
       </c>
       <c r="B4" t="str">
-        <v>PB223-156.25M</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Pericom Timing</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Franchise available</v>
+        <v>Americas</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>59</v>
+      <c r="A5" t="str">
+        <v>Inventory Management Partners</v>
       </c>
       <c r="B5" t="str">
-        <v>0039295243</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Molex Connector</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Franchise available</v>
+        <v>Americas</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>61</v>
+      <c r="A6" t="str">
+        <v>Atlantic Semiconductor Corp.</v>
       </c>
       <c r="B6" t="str">
-        <v>146839-4</v>
-      </c>
-      <c r="C6" t="str">
-        <v>TE Connector</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Limited (22 pcs)</v>
+        <v>Americas</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>64</v>
+      <c r="A7" t="str">
+        <v>Prism Electronics</v>
       </c>
       <c r="B7" t="str">
-        <v>5SGXMABK3H40C2N</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Intel FPGA</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Franchise available</v>
+        <v>Americas</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>79</v>
+      <c r="A8" t="str">
+        <v>Ganir Tech Ltd.</v>
       </c>
       <c r="B8" t="str">
-        <v>GMC32X5R226M16NT</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Murata Cap</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Limited</v>
+        <v>Europe</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>84</v>
+      <c r="A9" t="str">
+        <v>Abstract Electronics</v>
       </c>
       <c r="B9" t="str">
-        <v>KGM32LR50J476KU</v>
-      </c>
-      <c r="C9" t="str">
-        <v>KYOCERA Cap</v>
-      </c>
-      <c r="D9" t="str">
-        <v>None</v>
+        <v>Americas</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>85</v>
+      <c r="A10" t="str">
+        <v>ComSIT Distribution GmbH</v>
       </c>
       <c r="B10" t="str">
-        <v>KGM32LR51C226ML</v>
-      </c>
-      <c r="C10" t="str">
-        <v>KYOCERA Cap</v>
-      </c>
-      <c r="D10" t="str">
-        <v>None</v>
+        <v>Europe</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>96</v>
+      <c r="A11" t="str">
+        <v>GC Components Ltd</v>
       </c>
       <c r="B11" t="str">
-        <v>SI5341B-D-GM</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Silicon Labs Clock</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Limited (26 pcs)</v>
+        <v>Europe</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>97</v>
+      <c r="A12" t="str">
+        <v>Voyager Components</v>
       </c>
       <c r="B12" t="str">
-        <v>SMS1105GC</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Skyworks</v>
-      </c>
-      <c r="D12" t="str">
-        <v>None</v>
+        <v>Americas</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>98</v>
+      <c r="A13" t="str">
+        <v>LIBRA Elektronik GmbH</v>
       </c>
       <c r="B13" t="str">
-        <v>SST38VF6401-90-5I-B3K-E</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Microchip Flash</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Limited (89 pcs)</v>
+        <v>Europe</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>IC-Tronix Inc.</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SVT</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Eurodis Components</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PC Components (PCC)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Semi Source Inc.</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Converge LLC</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Hybrid Electronics</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Touchstone Systems, LLC</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Quest Components</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Electronic Stock Ltd.</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>J2 Sourcing AB</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Fly Chips</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SM Elektronik</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Schukat Electronic GmbH</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Maritex Leszek Losin Sp. j.</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>NexGen Digital, Inc.</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Chip Stock, LLC</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SIE Connect-GreenChips</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TME</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Right Parts</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Grossenbacher Systeme AG</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Goldney Electronics S.L.</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Sogenti GmbH</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Tectiva</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>CCI Europe GmbH</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Select Technology Inc.</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Semitech Inc.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tomark Electronics Ltd</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Husky Intl. Electronics, Inc.</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Microfarads</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>YBS Enterprises dbElectro-Comm</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Inelco Components S.L.</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>EXC GmbH</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>CHANETECH</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>A&amp;K Electronics</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Eptix Inc.</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TCX Micro S.L.</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>D.F. Sales Company</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>North Shore Components Inc.</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>New Advantage Corp</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Commodity Components</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Nexus Electronics LLC</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>BESA Technologies GmbH</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>iget Electronics GmbH</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Elcom Components, Inc.</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SPM Sales and Solution</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Prestocom, Ltd.</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Integrated Electronics Company</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Classic Components</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TerraBlock (fka Vecsys)</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>IBH Elektrotechnik GmbH</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>AG Electronics Limited</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Ashlea Components Ltd.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>FCC (First Choice Components)</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Quantum Digital Technology</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Smith &amp; Associates</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>AER Worldwide</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>FreedomUSA</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>P&amp;A Components Inc.</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>J.M.P. Electronics, Ltd.</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>HZD GmbH</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Lemkor Electronics, Inc</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Carlin Systems Inc.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>I.C. Plus, Inc.</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Demand Components</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>NetSource Technology Inc.</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Partservice</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Component Sense</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Megastar Electronics, Inc.</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>X-Press Micro, Inc.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Solsta Limited</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>RLX Solutions Inc.</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Impact Components</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Sonicare Solutions</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>4Source Electronics AG</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Weisbauer Elektronik GmbH</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Rapid Electronics Ltd.</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Zilex Electronics Inc.</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Silicon Solutions Inc.</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Diverse Electronics</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>AES - Atlas Electronic Systems</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Silicon Solutions LP Europe</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Merefields Electronics</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>A-Source Electronics BV</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Aitech Systems Ltd.</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Flex-Com International Ltd.</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Seba Components</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>AGS Devices Ltd</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Computer Components Ltd</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>CVC Components Ltd.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Omega GTI</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>AED Inc.</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>SECO spa</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>ICL Electronic-Bauteil-Service</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Dot Comps Electronics Inc.</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Dark Horse Electronics</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Tencell</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Sternenhof Electronics</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C111"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B36"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>MPN</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RFQ Count</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>MAX3221EEAE</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>16TQC100M</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MSP430F149IPM</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BCM5241A1IMLG</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>EP5358LUI</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LS14250</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PCA9517DP</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AQY210S</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PCA9517ADP</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LT3080EDD-1</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>EPM2210F324I5N</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>FTSH-108-01-L-DV</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HX1188FNL</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>NFM18PC105R0J3D</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>12106D476KAT2A</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>146839-3</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>J1011F21PNL</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TPS63060DSCT</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LT3070EUFD</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LTC4357IMS8</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>MAX3318EIPW</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CY29946AXC</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>FTLX8571D3BCV</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>MIC49500WR</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TPS63060DSC</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>ADG734BRUZ</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>LT1618EDD</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>LT3973IMSE</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>LTC4263IDE</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>C1005X5R1C104K</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>AFBR-709DMZ</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>MT28FW02GBBA1HPC-0AAT</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>S102M59Z5UU83L0R</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>LTM8026IV</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CY8C3866AXI-040</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B36"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>RFQ 1130350 Sourcing Statistics</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Total RFQs Sent</v>
+      </c>
+      <c r="B3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Unique Suppliers</v>
+      </c>
+      <c r="B4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Unique MPNs Sourced</v>
+      </c>
+      <c r="B5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>By Region</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="B8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="B9">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>